--- a/etf_holdings/2026-10-15_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-15_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-15 21:33:37</t>
+          <t>2026-10-15 22:10:45</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,17 +509,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-2.01%2440</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-2.01%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2440</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-15 21:33:37</t>
+          <t>2026-10-15 22:10:45</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -572,17 +572,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-7.25%5120</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-7.25%</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5120</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.62%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-15 21:33:37</t>
+          <t>2026-10-15 22:10:45</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -635,17 +635,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-6.93%4165</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-6.93%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4165</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.56%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-15 21:33:37</t>
+          <t>2026-10-15 22:10:45</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -698,17 +698,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-9.28%1075</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-9.28%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1075</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.74%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-15 21:33:37</t>
+          <t>2026-10-15 22:10:45</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -761,17 +761,17 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-6.94%3085</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-6.94%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.50%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-15 21:33:37</t>
+          <t>2026-10-15 22:10:45</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -824,17 +824,17 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-4.31%6765</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-4.31%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6765</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-15 21:33:37</t>
+          <t>2026-10-15 22:10:45</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -887,17 +887,17 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-8.61%573</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-8.61%</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>573</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.45%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-15 21:33:37</t>
+          <t>2026-10-15 22:10:45</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -950,17 +950,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-9.94%5300</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-9.94%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5300</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.52%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-15 21:33:37</t>
+          <t>2026-10-15 22:10:45</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1013,17 +1013,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-4.88%1950</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-4.88%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-15 21:33:37</t>
+          <t>2026-10-15 22:10:45</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1076,17 +1076,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-8.68%1630</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-8.68%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-15 21:33:37</t>
+          <t>2026-10-15 22:10:45</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1139,17 +1139,17 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-5.94%1345</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-5.94%</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1345</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-15 21:33:37</t>
+          <t>2026-10-15 22:10:45</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1202,17 +1202,17 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-6.34%1625</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-6.34%</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1625</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-15 21:33:37</t>
+          <t>2026-10-15 22:10:45</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-5.99%133.5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-5.99%</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-15 21:33:37</t>
+          <t>2026-10-15 22:10:45</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1328,17 +1328,17 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-5.56%1190</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-5.56%</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1190</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-15 21:33:42</t>
+          <t>2026-10-15 22:10:47</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-15 21:33:42</t>
+          <t>2026-10-15 22:10:47</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-15 21:33:42</t>
+          <t>2026-10-15 22:10:47</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-15 21:33:42</t>
+          <t>2026-10-15 22:10:47</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-15 21:33:42</t>
+          <t>2026-10-15 22:10:47</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-15 21:33:42</t>
+          <t>2026-10-15 22:10:47</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-15 21:33:42</t>
+          <t>2026-10-15 22:10:47</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-15 21:33:42</t>
+          <t>2026-10-15 22:10:47</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-15 21:33:42</t>
+          <t>2026-10-15 22:10:47</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-15 21:33:42</t>
+          <t>2026-10-15 22:10:47</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-15 21:33:42</t>
+          <t>2026-10-15 22:10:47</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-15 21:33:42</t>
+          <t>2026-10-15 22:10:47</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-15 21:33:42</t>
+          <t>2026-10-15 22:10:47</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-15 21:33:42</t>
+          <t>2026-10-15 22:10:47</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-15 21:33:42</t>
+          <t>2026-10-15 22:10:47</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-15 21:33:43</t>
+          <t>2026-10-15 22:10:50</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-15 21:33:43</t>
+          <t>2026-10-15 22:10:50</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-15 21:33:43</t>
+          <t>2026-10-15 22:10:50</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-15 21:33:43</t>
+          <t>2026-10-15 22:10:50</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-15 21:33:43</t>
+          <t>2026-10-15 22:10:50</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-15 21:33:43</t>
+          <t>2026-10-15 22:10:50</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-15 21:33:43</t>
+          <t>2026-10-15 22:10:50</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-15 21:33:43</t>
+          <t>2026-10-15 22:10:50</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-15 21:33:43</t>
+          <t>2026-10-15 22:10:50</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-15 21:33:43</t>
+          <t>2026-10-15 22:10:50</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-15 21:33:43</t>
+          <t>2026-10-15 22:10:50</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-15 21:33:43</t>
+          <t>2026-10-15 22:10:50</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-15 21:33:43</t>
+          <t>2026-10-15 22:10:50</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-15 21:33:43</t>
+          <t>2026-10-15 22:10:50</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-15 21:33:43</t>
+          <t>2026-10-15 22:10:50</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-15 21:33:44</t>
+          <t>2026-10-15 22:10:52</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-15 21:33:44</t>
+          <t>2026-10-15 22:10:52</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-15 21:33:44</t>
+          <t>2026-10-15 22:10:52</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-15 21:33:44</t>
+          <t>2026-10-15 22:10:52</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-15 21:33:44</t>
+          <t>2026-10-15 22:10:52</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-15 21:33:44</t>
+          <t>2026-10-15 22:10:52</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
